--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
@@ -8,31 +8,44 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91F98C1-39CF-41A1-889C-3D7DE184FF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E6E7A4-4C57-41B9-A9D1-D0A587FE8E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Areá_Atuação" sheetId="2" r:id="rId1"/>
     <sheet name="Horas_Treinamento" sheetId="3" r:id="rId2"/>
     <sheet name="Tickets_Mês" sheetId="4" r:id="rId3"/>
-    <sheet name="Conjunto de Dados" sheetId="1" r:id="rId4"/>
+    <sheet name="4 (a" sheetId="6" r:id="rId4"/>
+    <sheet name="Conjunto de Dados" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Horas_Treinamento!$A$12:$A$15</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Horas_Treinamento!$B$11</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Horas_Treinamento!$B$12:$B$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Horas_Treinamento!$A$12:$A$15</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Horas_Treinamento!$B$11</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Horas_Treinamento!$B$12:$B$15</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Conjunto de Dados'!$C$2:$C$51</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
-    <pivotCache cacheId="17" r:id="rId6"/>
-    <pivotCache cacheId="35" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="30" r:id="rId9"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,8 +53,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -261,6 +296,78 @@
   <si>
     <t>64-73</t>
   </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Moda</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>Variância</t>
+  </si>
+  <si>
+    <t>Desv.Pad</t>
+  </si>
+  <si>
+    <t>Horas_T</t>
+  </si>
+  <si>
+    <t>Tickets_M</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Rótulos de Coluna</t>
+  </si>
+  <si>
+    <t>Média de Horas_Treinamento</t>
+  </si>
+  <si>
+    <t>5-10</t>
+  </si>
+  <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>15-20</t>
+  </si>
+  <si>
+    <t>20-25</t>
+  </si>
+  <si>
+    <t>25-30</t>
+  </si>
+  <si>
+    <t>30-35</t>
+  </si>
+  <si>
+    <t>35-40</t>
+  </si>
+  <si>
+    <t>Coef.Var</t>
+  </si>
+  <si>
+    <t>Minimo</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Maximo</t>
+  </si>
+  <si>
+    <t>Outlier</t>
+  </si>
 </sst>
 </file>
 
@@ -293,7 +400,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,6 +417,12 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor theme="6" tint="-0.249977111117893"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -428,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -505,112 +618,43 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="136">
+  <dxfs count="62">
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -673,157 +717,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -865,6 +759,24 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
@@ -881,6 +793,9 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -1684,6 +1599,586 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Conjunto de Dados'!$C$2:$C$51</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Conjunto de Dados'!$D$2:$D$51</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-29FC-42C9-953A-AD4D5D914A5D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="89618816"/>
+        <c:axId val="89621216"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="89618816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="89621216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="89621216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="89618816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1813,6 +2308,133 @@
 </cx:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.5</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Horas_Treinamento</a:t>
+            </a:r>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{D4D91967-98AB-4E1C-BD29-B7088BFE774C}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Tickets_Mês</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Tickets_Mês</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{0E9441BA-8F83-4008-AD8B-BC268B22FBE8}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1933,6 +2555,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -3430,6 +4172,1552 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -4265,6 +6553,86 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: A área que investe mais em treinamento é a área</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> de Dados. Sim, pois a área de Dados tem um número muito maior comparado ao resto das outras áreas.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
             <a:rPr lang="pt-BR" sz="1200" b="1">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -4311,6 +6679,37 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>. O que esses valores indicam sobre a homogeneidade da carga de trabalho entre os colaboradores?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R:</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4450,6 +6849,56 @@
             </a:rPr>
             <a:t> Qual variável apresenta maior dispersão relativa? </a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: A variável de Horas_Treinamento.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:br>
             <a:rPr lang="pt-BR" sz="1200">
               <a:solidFill>
@@ -4485,6 +6934,58 @@
             </a:rPr>
             <a:t> Em qual caso o gestor deve estar mais atento à variabilidade dos resultados? Justifique com base no CV.</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: No caso das Horas_Treinamento</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> pois ela é medida em horas sendo um estilo de contagem extenso.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr lvl="0"/>
@@ -4690,6 +7191,22 @@
             </a:rPr>
             <a:t> O que pode ser dito sobre essa correlação?</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:effectLst/>
           </a:endParaRPr>
@@ -4837,6 +7354,198 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>659693</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>18345</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>589138</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>193323</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Gráfico 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5008AA8D-7B8F-3372-5281-59253CB87785}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10742082" y="10291234"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>236359</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>39512</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>165804</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>16934</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Gráfico 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA4843D5-9CEF-3B74-CA38-7732E1AD786A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15624526" y="10312401"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123472</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>52917</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>129823</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18C8D1E2-D772-06B4-190E-FCB424500E26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5039,6 +7748,90 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46149.368189120367" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{ABF722EE-4CF4-4B1C-BA0F-A9F8BEE91CFB}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D51" sheet="Conjunto de Dados"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Área_Atuação" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Suporte"/>
+        <s v="Desenvolvimento"/>
+        <s v="Dados"/>
+        <s v="Infraestrutura"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Horas_Treinamento" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5" maxValue="40" count="37">
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="9.5"/>
+        <n v="12.5"/>
+        <n v="15.5"/>
+        <n v="17"/>
+        <n v="18.5"/>
+        <n v="20"/>
+        <n v="21.5"/>
+        <n v="15"/>
+        <n v="16.5"/>
+        <n v="18"/>
+        <n v="19.5"/>
+        <n v="21"/>
+        <n v="22.5"/>
+        <n v="24"/>
+        <n v="25.5"/>
+        <n v="27"/>
+        <n v="28.5"/>
+        <n v="6.5"/>
+        <n v="23"/>
+        <n v="24.5"/>
+        <n v="16"/>
+        <n v="17.5"/>
+        <n v="30"/>
+        <n v="40"/>
+        <n v="22"/>
+        <n v="26"/>
+        <n v="28"/>
+      </sharedItems>
+      <fieldGroup base="2">
+        <rangePr startNum="5" endNum="40" groupInterval="5"/>
+        <groupItems count="9">
+          <s v="&lt;5"/>
+          <s v="5-10"/>
+          <s v="10-15"/>
+          <s v="15-20"/>
+          <s v="20-25"/>
+          <s v="25-30"/>
+          <s v="30-35"/>
+          <s v="35-40"/>
+          <s v="&gt;40"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Tickets_Mês" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="14" maxValue="69"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
   <r>
@@ -5954,8 +8747,313 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <s v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="17"/>
+  </r>
+  <r>
+    <s v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <s v="5"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <s v="6"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="7"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="26"/>
+  </r>
+  <r>
+    <s v="8"/>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="29"/>
+  </r>
+  <r>
+    <s v="9"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="10"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="33"/>
+  </r>
+  <r>
+    <s v="11"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <s v="12"/>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="13"/>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="14"/>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="15"/>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="33"/>
+  </r>
+  <r>
+    <s v="16"/>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="17"/>
+    <x v="1"/>
+    <x v="13"/>
+    <n v="39"/>
+  </r>
+  <r>
+    <s v="18"/>
+    <x v="1"/>
+    <x v="14"/>
+    <n v="42"/>
+  </r>
+  <r>
+    <s v="19"/>
+    <x v="1"/>
+    <x v="15"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="20"/>
+    <x v="1"/>
+    <x v="16"/>
+    <n v="47"/>
+  </r>
+  <r>
+    <s v="21"/>
+    <x v="2"/>
+    <x v="17"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="22"/>
+    <x v="2"/>
+    <x v="18"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="23"/>
+    <x v="2"/>
+    <x v="19"/>
+    <n v="41"/>
+  </r>
+  <r>
+    <s v="24"/>
+    <x v="2"/>
+    <x v="20"/>
+    <n v="44"/>
+  </r>
+  <r>
+    <s v="25"/>
+    <x v="2"/>
+    <x v="21"/>
+    <n v="47"/>
+  </r>
+  <r>
+    <s v="26"/>
+    <x v="2"/>
+    <x v="22"/>
+    <n v="49"/>
+  </r>
+  <r>
+    <s v="27"/>
+    <x v="2"/>
+    <x v="23"/>
+    <n v="53"/>
+  </r>
+  <r>
+    <s v="28"/>
+    <x v="2"/>
+    <x v="24"/>
+    <n v="55"/>
+  </r>
+  <r>
+    <s v="29"/>
+    <x v="2"/>
+    <x v="25"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <s v="30"/>
+    <x v="2"/>
+    <x v="26"/>
+    <n v="61"/>
+  </r>
+  <r>
+    <s v="31"/>
+    <x v="3"/>
+    <x v="27"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <s v="32"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <s v="33"/>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="34"/>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="35"/>
+    <x v="3"/>
+    <x v="11"/>
+    <n v="29"/>
+  </r>
+  <r>
+    <s v="36"/>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="32"/>
+  </r>
+  <r>
+    <s v="37"/>
+    <x v="3"/>
+    <x v="12"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="38"/>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="39"/>
+    <x v="3"/>
+    <x v="19"/>
+    <n v="41"/>
+  </r>
+  <r>
+    <s v="40"/>
+    <x v="3"/>
+    <x v="15"/>
+    <n v="43"/>
+  </r>
+  <r>
+    <s v="41"/>
+    <x v="1"/>
+    <x v="28"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <s v="42"/>
+    <x v="1"/>
+    <x v="29"/>
+    <n v="53"/>
+  </r>
+  <r>
+    <s v="43"/>
+    <x v="0"/>
+    <x v="30"/>
+    <n v="37"/>
+  </r>
+  <r>
+    <s v="44"/>
+    <x v="0"/>
+    <x v="31"/>
+    <n v="40"/>
+  </r>
+  <r>
+    <s v="45"/>
+    <x v="2"/>
+    <x v="32"/>
+    <n v="65"/>
+  </r>
+  <r>
+    <s v="46"/>
+    <x v="2"/>
+    <x v="33"/>
+    <n v="69"/>
+  </r>
+  <r>
+    <s v="47"/>
+    <x v="3"/>
+    <x v="34"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <s v="48"/>
+    <x v="3"/>
+    <x v="23"/>
+    <n v="52"/>
+  </r>
+  <r>
+    <s v="49"/>
+    <x v="0"/>
+    <x v="35"/>
+    <n v="55"/>
+  </r>
+  <r>
+    <s v="50"/>
+    <x v="1"/>
+    <x v="36"/>
+    <n v="60"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0AE5F1B-184C-4294-8F80-F29859079035}" name="Tabela dinâmica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Areá_Atuação">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0AE5F1B-184C-4294-8F80-F29859079035}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Areá_Atuação">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -6011,26 +9109,26 @@
     <dataField name="fa" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="135">
+    <format dxfId="61">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="134">
+    <format dxfId="60">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="59">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="131">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="130">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6041,26 +9139,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="129">
+    <format dxfId="55">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="53">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="126">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="125">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="124">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6085,7 +9183,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBDA1712-40A2-422F-AB1E-FA1F59619E8E}" name="Tabela dinâmica6" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Horas_Treinamento">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBDA1712-40A2-422F-AB1E-FA1F59619E8E}" name="Tabela dinâmica6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Horas_Treinamento">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -6151,19 +9249,19 @@
     <dataField name="fa" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="1"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="111">
+    <format dxfId="49">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="48">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="109">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="46">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="107">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="4">
@@ -6175,10 +9273,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="106">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="105">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6189,7 +9287,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="42">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -6198,16 +9296,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="41">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="39">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="4">
@@ -6219,10 +9317,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6247,7 +9345,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23DAB6E2-B496-42BF-875C-17BBC8209793}" name="Tabela dinâmica12" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tickets_Mês">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23DAB6E2-B496-42BF-875C-17BBC8209793}" name="Tabela dinâmica12" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tickets_Mês">
   <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -6321,16 +9419,16 @@
     <dataField name="fa" fld="3" subtotal="count" showDataAs="runTotal" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="49">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="33">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="6">
@@ -6344,10 +9442,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6358,16 +9456,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="27">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="6">
@@ -6381,10 +9479,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6395,11 +9493,227 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="23">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
             <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0D9A32C-61A1-4FB1-A7DC-EC8CE499D156}" name="Tabela dinâmica5" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" numFmtId="164" showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Horas_Treinamento" fld="2" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <formats count="23">
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="7">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="7">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea field="1" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea field="2" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -7223,13 +10537,205 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D9EBD1-B91E-419B-88E1-89223DF55B6B}">
+  <dimension ref="A3:F12"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12">
+        <v>8.75</v>
+      </c>
+      <c r="D5" s="12">
+        <v>8</v>
+      </c>
+      <c r="E5" s="12">
+        <v>7</v>
+      </c>
+      <c r="F5" s="12">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12">
+        <v>12.5</v>
+      </c>
+      <c r="D6" s="12">
+        <v>12.5</v>
+      </c>
+      <c r="E6" s="12">
+        <v>12</v>
+      </c>
+      <c r="F6" s="27">
+        <v>12.272727272727273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="12">
+        <v>17.25</v>
+      </c>
+      <c r="C7" s="12">
+        <v>17</v>
+      </c>
+      <c r="D7" s="27">
+        <v>16.833333333333332</v>
+      </c>
+      <c r="E7" s="12">
+        <v>16.75</v>
+      </c>
+      <c r="F7" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="12">
+        <v>22.5</v>
+      </c>
+      <c r="C8" s="12">
+        <v>22.25</v>
+      </c>
+      <c r="D8" s="12">
+        <v>22</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="12">
+        <v>27</v>
+      </c>
+      <c r="C9" s="12">
+        <v>28</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="12">
+        <v>30</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="12">
+        <v>40</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="27">
+        <v>23.958333333333332</v>
+      </c>
+      <c r="C12" s="27">
+        <v>17.153846153846153</v>
+      </c>
+      <c r="D12" s="27">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="E12" s="27">
+        <v>11.884615384615385</v>
+      </c>
+      <c r="F12" s="12">
+        <v>16.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:AB127"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="15" max="15" width="9.25" customWidth="1"/>
+    <col min="21" max="21" width="18.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -7680,7 +11186,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
@@ -7694,7 +11200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -7708,7 +11214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -7722,7 +11228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -7736,7 +11242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -7750,7 +11256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
@@ -7764,7 +11270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -7778,7 +11284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -7792,7 +11298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -7805,8 +11311,13 @@
       <c r="D41" s="6">
         <v>43</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -7819,8 +11330,13 @@
       <c r="D42" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -7833,8 +11349,13 @@
       <c r="D43" s="6">
         <v>53</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -7847,8 +11368,19 @@
       <c r="D44" s="6">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -7861,8 +11393,19 @@
       <c r="D45" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -7875,8 +11418,19 @@
       <c r="D46" s="6">
         <v>65</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -7889,8 +11443,19 @@
       <c r="D47" s="6">
         <v>69</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -7903,8 +11468,19 @@
       <c r="D48" s="6">
         <v>48</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -7917,8 +11493,19 @@
       <c r="D49" s="6">
         <v>52</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -7931,8 +11518,19 @@
       <c r="D50" s="6">
         <v>55</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>57</v>
       </c>
@@ -7945,6 +11543,1449 @@
       <c r="D51" s="7">
         <v>60</v>
       </c>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F52" s="26">
+        <v>4</v>
+      </c>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="26">
+        <v>6</v>
+      </c>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="11"/>
+      <c r="V52" s="11"/>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F53" s="11"/>
+      <c r="G53" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="I53" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="J53" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="L53" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="11"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F54" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G54" s="29">
+        <f>AVERAGE(C2:C51)</f>
+        <v>16.86</v>
+      </c>
+      <c r="H54" s="28" cm="1">
+        <f t="array" ref="H54:H56">_xlfn.MODE.MULT(C2:C51)</f>
+        <v>8</v>
+      </c>
+      <c r="I54" s="29">
+        <f>MEDIAN(C2:C51)</f>
+        <v>16.25</v>
+      </c>
+      <c r="J54" s="30">
+        <f>_xlfn.VAR.S(C2:C51)</f>
+        <v>54.775918367346947</v>
+      </c>
+      <c r="K54" s="30">
+        <f>_xlfn.STDEV.S(C2:C51)</f>
+        <v>7.4010754872077174</v>
+      </c>
+      <c r="L54" s="30">
+        <f>K54/G54 *100</f>
+        <v>43.897244882608049</v>
+      </c>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="28">
+        <v>11</v>
+      </c>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="11"/>
+      <c r="V55" s="11"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="31">
+        <v>14</v>
+      </c>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="11"/>
+      <c r="V56" s="11"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F57" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G57" s="33">
+        <f>AVERAGE(D2:D51)</f>
+        <v>38</v>
+      </c>
+      <c r="H57" s="28" cm="1">
+        <f t="array" ref="H57:H68">_xlfn.MODE.MULT(D2:D51)</f>
+        <v>21</v>
+      </c>
+      <c r="I57" s="33">
+        <f>MEDIAN(D2:D51)</f>
+        <v>37.5</v>
+      </c>
+      <c r="J57" s="30">
+        <f>_xlfn.VAR.S(D2:D51)</f>
+        <v>187.67346938775509</v>
+      </c>
+      <c r="K57" s="30">
+        <f>_xlfn.STDEV.S(D2:D51)</f>
+        <v>13.699396679699259</v>
+      </c>
+      <c r="L57" s="30">
+        <f>K57/G57 * 100</f>
+        <v>36.051043893945419</v>
+      </c>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="32">
+        <v>22</v>
+      </c>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
+      <c r="T58" s="11"/>
+      <c r="U58" s="11"/>
+      <c r="V58" s="11"/>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="28">
+        <v>29</v>
+      </c>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="11"/>
+      <c r="V59" s="11"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="28">
+        <v>30</v>
+      </c>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="11"/>
+      <c r="V60" s="11"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="28">
+        <v>33</v>
+      </c>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="11"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="28">
+        <v>24</v>
+      </c>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="11"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="11"/>
+      <c r="V62" s="11"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="28">
+        <v>47</v>
+      </c>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="O63" s="11"/>
+      <c r="P63" s="11"/>
+      <c r="Q63" s="11"/>
+      <c r="R63" s="11"/>
+      <c r="S63" s="11"/>
+      <c r="T63" s="11"/>
+      <c r="U63" s="11"/>
+      <c r="V63" s="11"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="28">
+        <v>35</v>
+      </c>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="O64" s="11"/>
+      <c r="P64" s="11"/>
+      <c r="Q64" s="11"/>
+      <c r="R64" s="11"/>
+      <c r="S64" s="11"/>
+      <c r="T64" s="11"/>
+      <c r="U64" s="11"/>
+      <c r="V64" s="11"/>
+    </row>
+    <row r="65" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="28">
+        <v>38</v>
+      </c>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="11"/>
+      <c r="S65" s="11"/>
+      <c r="T65" s="11"/>
+      <c r="U65" s="11"/>
+      <c r="V65" s="11"/>
+    </row>
+    <row r="66" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="28">
+        <v>41</v>
+      </c>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="11"/>
+      <c r="V66" s="11"/>
+    </row>
+    <row r="67" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="28">
+        <v>53</v>
+      </c>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="11"/>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="11"/>
+      <c r="T67" s="11"/>
+      <c r="U67" s="11"/>
+      <c r="V67" s="11"/>
+    </row>
+    <row r="68" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="28">
+        <v>55</v>
+      </c>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q68" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="R68" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="S68" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="T68" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="U68" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="V68" s="11"/>
+    </row>
+    <row r="69" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="O69" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="P69" s="28">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="28">
+        <v>11</v>
+      </c>
+      <c r="R69" s="28">
+        <v>16</v>
+      </c>
+      <c r="S69" s="28">
+        <v>22.1</v>
+      </c>
+      <c r="T69" s="28">
+        <v>30</v>
+      </c>
+      <c r="U69" s="30">
+        <f>STANDARDIZE(40,G54,K54)</f>
+        <v>3.1265726231270037</v>
+      </c>
+      <c r="V69" s="11"/>
+      <c r="W69" s="11"/>
+      <c r="X69" s="11"/>
+      <c r="Y69" s="11"/>
+      <c r="Z69" s="11"/>
+      <c r="AA69" s="11"/>
+      <c r="AB69" s="11"/>
+    </row>
+    <row r="70" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="O70" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="P70" s="28">
+        <v>14</v>
+      </c>
+      <c r="Q70" s="28">
+        <v>27</v>
+      </c>
+      <c r="R70" s="28">
+        <v>38</v>
+      </c>
+      <c r="S70" s="28">
+        <v>48</v>
+      </c>
+      <c r="T70" s="28">
+        <v>69</v>
+      </c>
+      <c r="U70" s="11"/>
+      <c r="V70" s="11"/>
+      <c r="W70" s="11"/>
+      <c r="X70" s="11"/>
+      <c r="Y70" s="11"/>
+      <c r="Z70" s="11"/>
+      <c r="AA70" s="11"/>
+      <c r="AB70" s="11"/>
+    </row>
+    <row r="71" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="P71" s="11"/>
+      <c r="Q71" s="11"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="11"/>
+      <c r="T71" s="11"/>
+      <c r="U71" s="11"/>
+      <c r="V71" s="11"/>
+      <c r="W71" s="11"/>
+      <c r="X71" s="11"/>
+      <c r="Y71" s="11"/>
+      <c r="Z71" s="11"/>
+      <c r="AA71" s="11"/>
+      <c r="AB71" s="11"/>
+    </row>
+    <row r="72" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F72" s="26">
+        <v>7</v>
+      </c>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="11"/>
+      <c r="U72" s="11"/>
+      <c r="V72" s="11"/>
+      <c r="W72" s="11"/>
+      <c r="X72" s="11"/>
+      <c r="Y72" s="11"/>
+      <c r="Z72" s="11"/>
+      <c r="AA72" s="11"/>
+      <c r="AB72" s="11"/>
+    </row>
+    <row r="73" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="11"/>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="11"/>
+      <c r="T73" s="11"/>
+      <c r="U73" s="11"/>
+      <c r="V73" s="11"/>
+      <c r="W73" s="11"/>
+      <c r="X73" s="11"/>
+      <c r="Y73" s="11"/>
+      <c r="Z73" s="11"/>
+      <c r="AA73" s="11"/>
+      <c r="AB73" s="11"/>
+    </row>
+    <row r="74" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="11"/>
+      <c r="U74" s="11"/>
+      <c r="V74" s="11"/>
+      <c r="W74" s="11"/>
+      <c r="X74" s="11"/>
+      <c r="Y74" s="11"/>
+      <c r="Z74" s="11"/>
+      <c r="AA74" s="11"/>
+      <c r="AB74" s="11"/>
+    </row>
+    <row r="75" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="11"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="11"/>
+      <c r="V75" s="11"/>
+      <c r="W75" s="11"/>
+      <c r="X75" s="11"/>
+      <c r="Y75" s="11"/>
+      <c r="Z75" s="11"/>
+      <c r="AA75" s="11"/>
+      <c r="AB75" s="11"/>
+    </row>
+    <row r="76" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="11"/>
+      <c r="X76" s="11"/>
+      <c r="Y76" s="11"/>
+      <c r="Z76" s="11"/>
+      <c r="AA76" s="11"/>
+      <c r="AB76" s="11"/>
+    </row>
+    <row r="77" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="11"/>
+      <c r="Q77" s="11"/>
+      <c r="R77" s="11"/>
+      <c r="S77" s="11"/>
+      <c r="T77" s="11"/>
+      <c r="U77" s="11"/>
+      <c r="V77" s="11"/>
+      <c r="W77" s="11"/>
+      <c r="X77" s="11"/>
+      <c r="Y77" s="11"/>
+      <c r="Z77" s="11"/>
+      <c r="AA77" s="11"/>
+      <c r="AB77" s="11"/>
+    </row>
+    <row r="78" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="11"/>
+      <c r="O78" s="11"/>
+      <c r="P78" s="11"/>
+      <c r="Q78" s="11"/>
+      <c r="R78" s="11"/>
+      <c r="S78" s="11"/>
+      <c r="T78" s="11"/>
+      <c r="U78" s="11"/>
+      <c r="V78" s="11"/>
+      <c r="W78" s="11"/>
+      <c r="X78" s="11"/>
+      <c r="Y78" s="11"/>
+      <c r="Z78" s="11"/>
+      <c r="AA78" s="11"/>
+      <c r="AB78" s="11"/>
+    </row>
+    <row r="79" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="11"/>
+      <c r="O79" s="11"/>
+      <c r="P79" s="11"/>
+      <c r="Q79" s="11"/>
+      <c r="R79" s="11"/>
+      <c r="S79" s="11"/>
+      <c r="T79" s="11"/>
+      <c r="U79" s="11"/>
+      <c r="V79" s="11"/>
+      <c r="W79" s="11"/>
+      <c r="X79" s="11"/>
+      <c r="Y79" s="11"/>
+      <c r="Z79" s="11"/>
+      <c r="AA79" s="11"/>
+      <c r="AB79" s="11"/>
+    </row>
+    <row r="80" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="11"/>
+      <c r="P80" s="11"/>
+      <c r="Q80" s="11"/>
+      <c r="R80" s="11"/>
+      <c r="S80" s="11"/>
+      <c r="T80" s="11"/>
+      <c r="U80" s="11"/>
+      <c r="V80" s="11"/>
+      <c r="W80" s="11"/>
+      <c r="X80" s="11"/>
+      <c r="Y80" s="11"/>
+      <c r="Z80" s="11"/>
+      <c r="AA80" s="11"/>
+      <c r="AB80" s="11"/>
+    </row>
+    <row r="81" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="11"/>
+      <c r="O81" s="11"/>
+      <c r="P81" s="11"/>
+      <c r="Q81" s="11"/>
+      <c r="R81" s="11"/>
+      <c r="S81" s="11"/>
+    </row>
+    <row r="82" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="11"/>
+      <c r="O82" s="11"/>
+      <c r="P82" s="11"/>
+      <c r="Q82" s="11"/>
+      <c r="R82" s="11"/>
+      <c r="S82" s="11"/>
+    </row>
+    <row r="83" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11"/>
+      <c r="P83" s="11"/>
+      <c r="Q83" s="11"/>
+      <c r="R83" s="11"/>
+      <c r="S83" s="11"/>
+    </row>
+    <row r="84" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+      <c r="N84" s="11"/>
+      <c r="O84" s="11"/>
+      <c r="P84" s="11"/>
+      <c r="Q84" s="11"/>
+      <c r="R84" s="11"/>
+      <c r="S84" s="11"/>
+    </row>
+    <row r="85" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
+      <c r="N85" s="11"/>
+      <c r="O85" s="11"/>
+      <c r="P85" s="11"/>
+      <c r="Q85" s="11"/>
+      <c r="R85" s="11"/>
+      <c r="S85" s="11"/>
+    </row>
+    <row r="86" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
+      <c r="N86" s="11"/>
+      <c r="O86" s="11"/>
+      <c r="P86" s="11"/>
+      <c r="Q86" s="11"/>
+      <c r="R86" s="11"/>
+      <c r="S86" s="11"/>
+    </row>
+    <row r="87" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="11"/>
+      <c r="M87" s="11"/>
+      <c r="N87" s="11"/>
+      <c r="O87" s="11"/>
+      <c r="P87" s="11"/>
+      <c r="Q87" s="11"/>
+      <c r="R87" s="11"/>
+      <c r="S87" s="11"/>
+    </row>
+    <row r="88" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
+      <c r="N88" s="11"/>
+      <c r="O88" s="11"/>
+      <c r="P88" s="11"/>
+      <c r="Q88" s="11"/>
+      <c r="R88" s="11"/>
+      <c r="S88" s="11"/>
+    </row>
+    <row r="89" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="11"/>
+      <c r="M89" s="11"/>
+      <c r="N89" s="11"/>
+      <c r="O89" s="11"/>
+      <c r="P89" s="11"/>
+      <c r="Q89" s="11"/>
+      <c r="R89" s="11"/>
+      <c r="S89" s="11"/>
+    </row>
+    <row r="90" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
+      <c r="N90" s="11"/>
+      <c r="O90" s="11"/>
+      <c r="P90" s="11"/>
+      <c r="Q90" s="11"/>
+      <c r="R90" s="11"/>
+      <c r="S90" s="11"/>
+    </row>
+    <row r="91" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
+      <c r="N91" s="11"/>
+      <c r="O91" s="11"/>
+      <c r="P91" s="11"/>
+      <c r="Q91" s="11"/>
+      <c r="R91" s="11"/>
+      <c r="S91" s="11"/>
+    </row>
+    <row r="92" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
+      <c r="N92" s="11"/>
+      <c r="O92" s="11"/>
+      <c r="P92" s="11"/>
+      <c r="Q92" s="11"/>
+      <c r="R92" s="11"/>
+      <c r="S92" s="11"/>
+    </row>
+    <row r="93" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="11"/>
+      <c r="K93" s="11"/>
+      <c r="L93" s="11"/>
+      <c r="M93" s="11"/>
+      <c r="N93" s="11"/>
+      <c r="O93" s="11"/>
+      <c r="P93" s="11"/>
+      <c r="Q93" s="11"/>
+      <c r="R93" s="11"/>
+      <c r="S93" s="11"/>
+    </row>
+    <row r="94" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
+      <c r="N94" s="11"/>
+      <c r="O94" s="11"/>
+      <c r="P94" s="11"/>
+      <c r="Q94" s="11"/>
+      <c r="R94" s="11"/>
+      <c r="S94" s="11"/>
+    </row>
+    <row r="95" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
+      <c r="K95" s="11"/>
+      <c r="L95" s="11"/>
+      <c r="M95" s="11"/>
+      <c r="N95" s="11"/>
+      <c r="O95" s="11"/>
+      <c r="P95" s="11"/>
+      <c r="Q95" s="11"/>
+      <c r="R95" s="11"/>
+      <c r="S95" s="11"/>
+    </row>
+    <row r="96" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
+      <c r="N96" s="11"/>
+      <c r="O96" s="11"/>
+      <c r="P96" s="11"/>
+      <c r="Q96" s="11"/>
+      <c r="R96" s="11"/>
+      <c r="S96" s="11"/>
+    </row>
+    <row r="97" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
+      <c r="K97" s="11"/>
+      <c r="L97" s="11"/>
+      <c r="M97" s="11"/>
+      <c r="N97" s="11"/>
+      <c r="O97" s="11"/>
+      <c r="P97" s="11"/>
+      <c r="Q97" s="11"/>
+      <c r="R97" s="11"/>
+      <c r="S97" s="11"/>
+    </row>
+    <row r="98" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
+      <c r="N98" s="11"/>
+      <c r="O98" s="11"/>
+      <c r="P98" s="11"/>
+      <c r="Q98" s="11"/>
+      <c r="R98" s="11"/>
+      <c r="S98" s="11"/>
+    </row>
+    <row r="99" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="11"/>
+      <c r="K99" s="11"/>
+      <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
+      <c r="N99" s="11"/>
+      <c r="O99" s="11"/>
+      <c r="P99" s="11"/>
+      <c r="Q99" s="11"/>
+      <c r="R99" s="11"/>
+      <c r="S99" s="11"/>
+    </row>
+    <row r="100" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="11"/>
+      <c r="K100" s="11"/>
+      <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
+      <c r="N100" s="11"/>
+      <c r="O100" s="11"/>
+      <c r="P100" s="11"/>
+      <c r="Q100" s="11"/>
+      <c r="R100" s="11"/>
+      <c r="S100" s="11"/>
+    </row>
+    <row r="101" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
+      <c r="K101" s="11"/>
+      <c r="L101" s="11"/>
+      <c r="M101" s="11"/>
+      <c r="N101" s="11"/>
+      <c r="O101" s="11"/>
+      <c r="P101" s="11"/>
+      <c r="Q101" s="11"/>
+      <c r="R101" s="11"/>
+      <c r="S101" s="11"/>
+    </row>
+    <row r="102" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="11"/>
+      <c r="K102" s="11"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
+      <c r="N102" s="11"/>
+      <c r="O102" s="11"/>
+      <c r="P102" s="11"/>
+      <c r="Q102" s="11"/>
+      <c r="R102" s="11"/>
+      <c r="S102" s="11"/>
+    </row>
+    <row r="103" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="11"/>
+      <c r="K103" s="11"/>
+      <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
+      <c r="N103" s="11"/>
+      <c r="O103" s="11"/>
+      <c r="P103" s="11"/>
+      <c r="Q103" s="11"/>
+      <c r="R103" s="11"/>
+      <c r="S103" s="11"/>
+    </row>
+    <row r="104" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F104" s="11"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="11"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="11"/>
+      <c r="K104" s="11"/>
+      <c r="L104" s="11"/>
+      <c r="M104" s="11"/>
+      <c r="N104" s="11"/>
+      <c r="O104" s="11"/>
+      <c r="P104" s="11"/>
+      <c r="Q104" s="11"/>
+      <c r="R104" s="11"/>
+      <c r="S104" s="11"/>
+    </row>
+    <row r="105" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="11"/>
+      <c r="K105" s="11"/>
+      <c r="L105" s="11"/>
+      <c r="M105" s="11"/>
+      <c r="N105" s="11"/>
+      <c r="O105" s="11"/>
+      <c r="P105" s="11"/>
+      <c r="Q105" s="11"/>
+      <c r="R105" s="11"/>
+      <c r="S105" s="11"/>
+    </row>
+    <row r="106" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="11"/>
+      <c r="K106" s="11"/>
+      <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
+      <c r="N106" s="11"/>
+      <c r="O106" s="11"/>
+      <c r="P106" s="11"/>
+      <c r="Q106" s="11"/>
+      <c r="R106" s="11"/>
+      <c r="S106" s="11"/>
+    </row>
+    <row r="107" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="11"/>
+      <c r="K107" s="11"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="11"/>
+      <c r="N107" s="11"/>
+      <c r="O107" s="11"/>
+      <c r="P107" s="11"/>
+      <c r="Q107" s="11"/>
+      <c r="R107" s="11"/>
+      <c r="S107" s="11"/>
+    </row>
+    <row r="108" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="11"/>
+      <c r="K108" s="11"/>
+      <c r="L108" s="11"/>
+      <c r="M108" s="11"/>
+      <c r="N108" s="11"/>
+      <c r="O108" s="11"/>
+      <c r="P108" s="11"/>
+      <c r="Q108" s="11"/>
+      <c r="R108" s="11"/>
+      <c r="S108" s="11"/>
+    </row>
+    <row r="109" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="11"/>
+      <c r="J109" s="11"/>
+      <c r="K109" s="11"/>
+      <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
+      <c r="N109" s="11"/>
+      <c r="O109" s="11"/>
+      <c r="P109" s="11"/>
+      <c r="Q109" s="11"/>
+      <c r="R109" s="11"/>
+      <c r="S109" s="11"/>
+    </row>
+    <row r="110" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="11"/>
+      <c r="K110" s="11"/>
+      <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
+      <c r="N110" s="11"/>
+      <c r="O110" s="11"/>
+      <c r="P110" s="11"/>
+      <c r="Q110" s="11"/>
+      <c r="R110" s="11"/>
+      <c r="S110" s="11"/>
+    </row>
+    <row r="111" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11"/>
+      <c r="K111" s="11"/>
+      <c r="L111" s="11"/>
+      <c r="M111" s="11"/>
+      <c r="N111" s="11"/>
+      <c r="O111" s="11"/>
+      <c r="P111" s="11"/>
+      <c r="Q111" s="11"/>
+      <c r="R111" s="11"/>
+      <c r="S111" s="11"/>
+    </row>
+    <row r="112" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="11"/>
+      <c r="K112" s="11"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
+      <c r="N112" s="11"/>
+      <c r="O112" s="11"/>
+      <c r="P112" s="11"/>
+      <c r="Q112" s="11"/>
+      <c r="R112" s="11"/>
+      <c r="S112" s="11"/>
+    </row>
+    <row r="113" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F113" s="11"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="11"/>
+      <c r="K113" s="11"/>
+      <c r="L113" s="11"/>
+      <c r="M113" s="11"/>
+      <c r="N113" s="11"/>
+      <c r="O113" s="11"/>
+      <c r="P113" s="11"/>
+      <c r="Q113" s="11"/>
+      <c r="R113" s="11"/>
+      <c r="S113" s="11"/>
+    </row>
+    <row r="114" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="11"/>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="11"/>
+      <c r="P114" s="11"/>
+      <c r="Q114" s="11"/>
+      <c r="R114" s="11"/>
+      <c r="S114" s="11"/>
+    </row>
+    <row r="115" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="11"/>
+      <c r="K115" s="11"/>
+      <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
+      <c r="N115" s="11"/>
+      <c r="O115" s="11"/>
+      <c r="P115" s="11"/>
+      <c r="Q115" s="11"/>
+      <c r="R115" s="11"/>
+      <c r="S115" s="11"/>
+    </row>
+    <row r="116" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="11"/>
+      <c r="K116" s="11"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
+      <c r="N116" s="11"/>
+      <c r="O116" s="11"/>
+      <c r="P116" s="11"/>
+      <c r="Q116" s="11"/>
+      <c r="R116" s="11"/>
+      <c r="S116" s="11"/>
+    </row>
+    <row r="117" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="11"/>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
+      <c r="N117" s="11"/>
+      <c r="O117" s="11"/>
+      <c r="P117" s="11"/>
+      <c r="Q117" s="11"/>
+      <c r="R117" s="11"/>
+      <c r="S117" s="11"/>
+    </row>
+    <row r="118" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
+      <c r="H118" s="11"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="11"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11"/>
+      <c r="O118" s="11"/>
+      <c r="P118" s="11"/>
+      <c r="Q118" s="11"/>
+      <c r="R118" s="11"/>
+      <c r="S118" s="11"/>
+    </row>
+    <row r="119" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="11"/>
+      <c r="K119" s="11"/>
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
+      <c r="N119" s="11"/>
+      <c r="O119" s="11"/>
+      <c r="P119" s="11"/>
+      <c r="Q119" s="11"/>
+      <c r="R119" s="11"/>
+      <c r="S119" s="11"/>
+    </row>
+    <row r="120" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="11"/>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="11"/>
+      <c r="O120" s="11"/>
+      <c r="P120" s="11"/>
+      <c r="Q120" s="11"/>
+      <c r="R120" s="11"/>
+      <c r="S120" s="11"/>
+    </row>
+    <row r="121" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="11"/>
+      <c r="K121" s="11"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
+      <c r="N121" s="11"/>
+      <c r="O121" s="11"/>
+      <c r="P121" s="11"/>
+      <c r="Q121" s="11"/>
+      <c r="R121" s="11"/>
+      <c r="S121" s="11"/>
+    </row>
+    <row r="122" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="11"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="11"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="11"/>
+      <c r="P122" s="11"/>
+      <c r="Q122" s="11"/>
+      <c r="R122" s="11"/>
+      <c r="S122" s="11"/>
+    </row>
+    <row r="123" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+      <c r="H123" s="11"/>
+      <c r="I123" s="11"/>
+      <c r="J123" s="11"/>
+      <c r="K123" s="11"/>
+      <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
+      <c r="N123" s="11"/>
+      <c r="O123" s="11"/>
+      <c r="P123" s="11"/>
+      <c r="Q123" s="11"/>
+      <c r="R123" s="11"/>
+      <c r="S123" s="11"/>
+    </row>
+    <row r="124" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="11"/>
+      <c r="K124" s="11"/>
+      <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
+      <c r="N124" s="11"/>
+      <c r="O124" s="11"/>
+      <c r="P124" s="11"/>
+      <c r="Q124" s="11"/>
+      <c r="R124" s="11"/>
+      <c r="S124" s="11"/>
+    </row>
+    <row r="125" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="11"/>
+      <c r="K125" s="11"/>
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
+      <c r="N125" s="11"/>
+      <c r="O125" s="11"/>
+      <c r="P125" s="11"/>
+      <c r="Q125" s="11"/>
+      <c r="R125" s="11"/>
+      <c r="S125" s="11"/>
+    </row>
+    <row r="126" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="11"/>
+      <c r="I126" s="11"/>
+      <c r="J126" s="11"/>
+      <c r="K126" s="11"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+      <c r="N126" s="11"/>
+      <c r="O126" s="11"/>
+      <c r="P126" s="11"/>
+      <c r="Q126" s="11"/>
+      <c r="R126" s="11"/>
+      <c r="S126" s="11"/>
+    </row>
+    <row r="127" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11"/>
+      <c r="O127" s="11"/>
+      <c r="P127" s="11"/>
+      <c r="Q127" s="11"/>
+      <c r="R127" s="11"/>
+      <c r="S127" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Documents\GitHub\Arquivado\Faculdade\Terceiro Semestre\Estatística Aplicada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E6E7A4-4C57-41B9-A9D1-D0A587FE8E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A2A302-6F73-4EA5-9D5F-F929B6F6F67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Areá_Atuação" sheetId="2" r:id="rId1"/>
@@ -23,16 +23,15 @@
     <definedName name="_xlchart.v1.0" hidden="1">Horas_Treinamento!$A$12:$A$15</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Horas_Treinamento!$B$11</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Horas_Treinamento!$B$12:$B$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Conjunto de Dados'!$C$2:$C$51</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Conjunto de Dados'!$C$2:$C$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId6"/>
     <pivotCache cacheId="1" r:id="rId7"/>
     <pivotCache cacheId="2" r:id="rId8"/>
-    <pivotCache cacheId="30" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -76,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -368,6 +367,24 @@
   <si>
     <t>Outlier</t>
   </si>
+  <si>
+    <t>Coeficiente de Relação r</t>
+  </si>
+  <si>
+    <t>Correlação linear positiva forte</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
 </sst>
 </file>
 
@@ -541,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -640,6 +657,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1614,6 +1634,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Horas_Treinamento</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> x Tickets_Mês</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1674,6 +1724,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="pt-BR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Conjunto de Dados'!$C$2:$C$51</c:f>
@@ -2313,35 +2421,38 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:rich>
-          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Horas_Treinamento</a:t>
-            </a:r>
-          </a:p>
-        </cx:rich>
+        <cx:txData>
+          <cx:v>Horas_Treinamento</cx:v>
+        </cx:txData>
       </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Horas_Treinamento</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
@@ -5827,8 +5938,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3575050" y="527050"/>
-              <a:ext cx="5073650" cy="2882900"/>
+              <a:off x="3600450" y="533400"/>
+              <a:ext cx="5276850" cy="2936875"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7203,7 +7314,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>R:</a:t>
+            <a:t>R: Há uma correlação linear positiva forte, com o coeficiente de relação sendo 0,99.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -7274,18 +7385,6 @@
         </a:p>
         <a:p>
           <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
-          <a:r>
-            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:effectLst/>
           </a:endParaRPr>
@@ -7403,8 +7502,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10742082" y="10291234"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="10927643" y="10419645"/>
+              <a:ext cx="4749095" cy="2775303"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7481,8 +7580,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15624526" y="10312401"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="16705084" y="10440812"/>
+              <a:ext cx="4730045" cy="2777772"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7514,16 +7613,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123472</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>81139</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>131234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>52917</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>129823</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>108657</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9516,7 +9615,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0D9A32C-61A1-4FB1-A7DC-EC8CE499D156}" name="Tabela dinâmica5" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0D9A32C-61A1-4FB1-A7DC-EC8CE499D156}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -10054,15 +10153,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE768767-D7B5-4940-ACE8-9C4982467EE3}">
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>62</v>
       </c>
@@ -10076,7 +10175,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>37</v>
       </c>
@@ -10090,7 +10189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>26</v>
       </c>
@@ -10104,7 +10203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>44</v>
       </c>
@@ -10118,7 +10217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
@@ -10132,7 +10231,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>58</v>
       </c>
@@ -10144,7 +10243,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>62</v>
       </c>
@@ -10152,7 +10251,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>37</v>
       </c>
@@ -10160,7 +10259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
@@ -10168,7 +10267,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>44</v>
       </c>
@@ -10176,7 +10275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>5</v>
       </c>
@@ -10184,7 +10283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>58</v>
       </c>
@@ -10201,7 +10300,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1FA8A1-06B5-4FF8-8B14-81C20D53ECC7}">
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
@@ -10209,7 +10308,7 @@
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
@@ -10223,7 +10322,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>63</v>
       </c>
@@ -10237,7 +10336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>64</v>
       </c>
@@ -10251,7 +10350,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>65</v>
       </c>
@@ -10265,7 +10364,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>66</v>
       </c>
@@ -10279,7 +10378,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>58</v>
       </c>
@@ -10291,7 +10390,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>3</v>
       </c>
@@ -10299,7 +10398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>63</v>
       </c>
@@ -10307,7 +10406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>64</v>
       </c>
@@ -10315,7 +10414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>65</v>
       </c>
@@ -10323,7 +10422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>66</v>
       </c>
@@ -10331,7 +10430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>58</v>
       </c>
@@ -10348,15 +10447,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA27BDE-5BEF-44E2-8E70-AEAC1839CC4C}">
   <dimension ref="A3:D20"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -10370,7 +10469,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>67</v>
       </c>
@@ -10384,7 +10483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>68</v>
       </c>
@@ -10398,7 +10497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>69</v>
       </c>
@@ -10412,7 +10511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>70</v>
       </c>
@@ -10426,7 +10525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>71</v>
       </c>
@@ -10440,7 +10539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>72</v>
       </c>
@@ -10454,7 +10553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>58</v>
       </c>
@@ -10466,7 +10565,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>2</v>
       </c>
@@ -10474,7 +10573,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
         <v>67</v>
       </c>
@@ -10482,7 +10581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
         <v>68</v>
       </c>
@@ -10490,7 +10589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
         <v>69</v>
       </c>
@@ -10498,7 +10597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>70</v>
       </c>
@@ -10506,7 +10605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>71</v>
       </c>
@@ -10514,7 +10613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
         <v>72</v>
       </c>
@@ -10522,7 +10621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>58</v>
       </c>
@@ -10539,16 +10638,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D9EBD1-B91E-419B-88E1-89223DF55B6B}">
   <dimension ref="A3:F12"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>82</v>
       </c>
@@ -10560,7 +10659,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>80</v>
       </c>
@@ -10580,7 +10679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>83</v>
       </c>
@@ -10598,7 +10697,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>84</v>
       </c>
@@ -10616,7 +10715,7 @@
         <v>12.272727272727273</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>85</v>
       </c>
@@ -10636,7 +10735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>86</v>
       </c>
@@ -10654,7 +10753,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>87</v>
       </c>
@@ -10672,7 +10771,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>88</v>
       </c>
@@ -10686,7 +10785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>89</v>
       </c>
@@ -10700,7 +10799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>58</v>
       </c>
@@ -10728,17 +10827,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB127"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.625" customWidth="1"/>
     <col min="15" max="15" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="18.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -10752,7 +10851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10766,7 +10865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -10780,7 +10879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -10794,7 +10893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10808,7 +10907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -10822,7 +10921,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -10836,7 +10935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -10850,7 +10949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -10864,7 +10963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -10878,7 +10977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -10892,7 +10991,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -10906,7 +11005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -10920,7 +11019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -10934,7 +11033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -10948,7 +11047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -10962,7 +11061,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -10976,7 +11075,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -10990,7 +11089,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -11004,7 +11103,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -11018,7 +11117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -11032,7 +11131,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -11046,7 +11145,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -11060,7 +11159,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -11074,7 +11173,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
@@ -11088,7 +11187,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>14</v>
       </c>
@@ -11102,7 +11201,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
@@ -11116,7 +11215,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
@@ -11130,7 +11229,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
@@ -11144,7 +11243,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
@@ -11158,7 +11257,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -11172,7 +11271,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
@@ -11186,7 +11285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
@@ -11200,7 +11299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -11214,7 +11313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -11228,7 +11327,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -11242,7 +11341,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -11256,7 +11355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
@@ -11270,7 +11369,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -11284,7 +11383,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -11298,7 +11397,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -11317,7 +11416,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -11336,7 +11435,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -11355,7 +11454,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -11380,7 +11479,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -11405,7 +11504,7 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -11430,7 +11529,7 @@
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -11455,7 +11554,7 @@
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -11480,7 +11579,7 @@
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -11505,7 +11604,7 @@
       <c r="O49" s="11"/>
       <c r="P49" s="11"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -11530,7 +11629,7 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>57</v>
       </c>
@@ -11555,7 +11654,7 @@
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F52" s="26">
         <v>4</v>
       </c>
@@ -11578,7 +11677,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F53" s="11"/>
       <c r="G53" s="28" t="s">
         <v>73</v>
@@ -11609,7 +11708,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F54" s="28" t="s">
         <v>78</v>
       </c>
@@ -11648,7 +11747,7 @@
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
       <c r="H55" s="28">
@@ -11669,7 +11768,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="11"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F56" s="11"/>
       <c r="G56" s="11"/>
       <c r="H56" s="31">
@@ -11687,7 +11786,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F57" s="28" t="s">
         <v>79</v>
       </c>
@@ -11724,7 +11823,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="11"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
       <c r="H58" s="32">
@@ -11742,7 +11841,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
       <c r="H59" s="28">
@@ -11760,7 +11859,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F60" s="11"/>
       <c r="G60" s="11"/>
       <c r="H60" s="28">
@@ -11778,7 +11877,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
       <c r="H61" s="28">
@@ -11796,7 +11895,7 @@
       <c r="U61" s="11"/>
       <c r="V61" s="11"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F62" s="11"/>
       <c r="G62" s="11"/>
       <c r="H62" s="28">
@@ -11814,7 +11913,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
       <c r="H63" s="28">
@@ -11832,7 +11931,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F64" s="11"/>
       <c r="G64" s="11"/>
       <c r="H64" s="28">
@@ -11850,7 +11949,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="11"/>
     </row>
-    <row r="65" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="65" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
       <c r="H65" s="28">
@@ -11868,7 +11967,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
     </row>
-    <row r="66" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="66" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="H66" s="28">
@@ -11886,7 +11985,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="67" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F67" s="11"/>
       <c r="G67" s="11"/>
       <c r="H67" s="28">
@@ -11904,7 +12003,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="68" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F68" s="11"/>
       <c r="G68" s="11"/>
       <c r="H68" s="28">
@@ -11934,7 +12033,7 @@
       </c>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="69" spans="6:28" x14ac:dyDescent="0.25">
       <c r="O69" s="28" t="s">
         <v>78</v>
       </c>
@@ -11965,7 +12064,7 @@
       <c r="AA69" s="11"/>
       <c r="AB69" s="11"/>
     </row>
-    <row r="70" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="70" spans="6:28" x14ac:dyDescent="0.25">
       <c r="O70" s="28" t="s">
         <v>79</v>
       </c>
@@ -11993,7 +12092,7 @@
       <c r="AA70" s="11"/>
       <c r="AB70" s="11"/>
     </row>
-    <row r="71" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="71" spans="6:28" x14ac:dyDescent="0.25">
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
       <c r="R71" s="11"/>
@@ -12008,7 +12107,7 @@
       <c r="AA71" s="11"/>
       <c r="AB71" s="11"/>
     </row>
-    <row r="72" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="72" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F72" s="26">
         <v>7</v>
       </c>
@@ -12035,7 +12134,7 @@
       <c r="AA72" s="11"/>
       <c r="AB72" s="11"/>
     </row>
-    <row r="73" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="73" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F73" s="11"/>
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
@@ -12060,7 +12159,7 @@
       <c r="AA73" s="11"/>
       <c r="AB73" s="11"/>
     </row>
-    <row r="74" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="74" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F74" s="11"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
@@ -12085,7 +12184,7 @@
       <c r="AA74" s="11"/>
       <c r="AB74" s="11"/>
     </row>
-    <row r="75" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="75" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F75" s="11"/>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
@@ -12110,7 +12209,7 @@
       <c r="AA75" s="11"/>
       <c r="AB75" s="11"/>
     </row>
-    <row r="76" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="76" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F76" s="11"/>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
@@ -12135,7 +12234,7 @@
       <c r="AA76" s="11"/>
       <c r="AB76" s="11"/>
     </row>
-    <row r="77" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="77" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F77" s="11"/>
       <c r="G77" s="11"/>
       <c r="H77" s="11"/>
@@ -12160,7 +12259,7 @@
       <c r="AA77" s="11"/>
       <c r="AB77" s="11"/>
     </row>
-    <row r="78" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="78" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F78" s="11"/>
       <c r="G78" s="11"/>
       <c r="H78" s="11"/>
@@ -12185,7 +12284,7 @@
       <c r="AA78" s="11"/>
       <c r="AB78" s="11"/>
     </row>
-    <row r="79" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="79" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F79" s="11"/>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
@@ -12210,7 +12309,7 @@
       <c r="AA79" s="11"/>
       <c r="AB79" s="11"/>
     </row>
-    <row r="80" spans="6:28" x14ac:dyDescent="0.35">
+    <row r="80" spans="6:28" x14ac:dyDescent="0.25">
       <c r="F80" s="11"/>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
@@ -12235,7 +12334,7 @@
       <c r="AA80" s="11"/>
       <c r="AB80" s="11"/>
     </row>
-    <row r="81" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F81" s="11"/>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
@@ -12251,7 +12350,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="11"/>
     </row>
-    <row r="82" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F82" s="11"/>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
@@ -12267,7 +12366,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="11"/>
     </row>
-    <row r="83" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F83" s="11"/>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
@@ -12283,7 +12382,7 @@
       <c r="R83" s="11"/>
       <c r="S83" s="11"/>
     </row>
-    <row r="84" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F84" s="11"/>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
@@ -12299,7 +12398,7 @@
       <c r="R84" s="11"/>
       <c r="S84" s="11"/>
     </row>
-    <row r="85" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F85" s="11"/>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
@@ -12315,7 +12414,7 @@
       <c r="R85" s="11"/>
       <c r="S85" s="11"/>
     </row>
-    <row r="86" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F86" s="11"/>
       <c r="G86" s="11"/>
       <c r="H86" s="11"/>
@@ -12331,13 +12430,19 @@
       <c r="R86" s="11"/>
       <c r="S86" s="11"/>
     </row>
-    <row r="87" spans="6:19" x14ac:dyDescent="0.35">
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="11"/>
-      <c r="K87" s="11"/>
+    <row r="87" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F87" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="G87" s="34"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="28">
+        <f>CORREL(C2:C51,D2:D51)</f>
+        <v>0.99001168508891357</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>98</v>
+      </c>
       <c r="L87" s="11"/>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -12347,7 +12452,7 @@
       <c r="R87" s="11"/>
       <c r="S87" s="11"/>
     </row>
-    <row r="88" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F88" s="11"/>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
@@ -12363,15 +12468,23 @@
       <c r="R88" s="11"/>
       <c r="S88" s="11"/>
     </row>
-    <row r="89" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F89" s="11"/>
       <c r="G89" s="11"/>
-      <c r="H89" s="11"/>
-      <c r="I89" s="11"/>
+      <c r="H89" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-      <c r="M89" s="11"/>
+      <c r="L89" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M89" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="N89" s="11"/>
       <c r="O89" s="11"/>
       <c r="P89" s="11"/>
@@ -12379,15 +12492,27 @@
       <c r="R89" s="11"/>
       <c r="S89" s="11"/>
     </row>
-    <row r="90" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11"/>
-      <c r="I90" s="11"/>
+      <c r="G90" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H90" s="11" cm="1">
+        <f t="array" ref="H90:I90">LINEST(D2:D51,C2:C51)</f>
+        <v>1.8325124253917631</v>
+      </c>
+      <c r="I90" s="11">
+        <v>7.1038405078948763</v>
+      </c>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
-      <c r="M90" s="11"/>
+      <c r="L90" s="11">
+        <v>40</v>
+      </c>
+      <c r="M90" s="27">
+        <f>H90 *L90 + I90</f>
+        <v>80.404337523565388</v>
+      </c>
       <c r="N90" s="11"/>
       <c r="O90" s="11"/>
       <c r="P90" s="11"/>
@@ -12395,7 +12520,7 @@
       <c r="R90" s="11"/>
       <c r="S90" s="11"/>
     </row>
-    <row r="91" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F91" s="11"/>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
@@ -12411,7 +12536,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="11"/>
     </row>
-    <row r="92" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F92" s="11"/>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
@@ -12427,7 +12552,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="11"/>
     </row>
-    <row r="93" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F93" s="11"/>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
@@ -12443,7 +12568,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="11"/>
     </row>
-    <row r="94" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F94" s="11"/>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
@@ -12459,7 +12584,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="11"/>
     </row>
-    <row r="95" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F95" s="11"/>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
@@ -12475,7 +12600,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="11"/>
     </row>
-    <row r="96" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F96" s="11"/>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -12491,7 +12616,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="11"/>
     </row>
-    <row r="97" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F97" s="11"/>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
@@ -12507,7 +12632,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="11"/>
     </row>
-    <row r="98" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
@@ -12523,7 +12648,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="11"/>
     </row>
-    <row r="99" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F99" s="11"/>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
@@ -12539,7 +12664,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="11"/>
     </row>
-    <row r="100" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F100" s="11"/>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
@@ -12555,7 +12680,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="11"/>
     </row>
-    <row r="101" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F101" s="11"/>
       <c r="G101" s="11"/>
       <c r="H101" s="11"/>
@@ -12571,7 +12696,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="11"/>
     </row>
-    <row r="102" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F102" s="11"/>
       <c r="G102" s="11"/>
       <c r="H102" s="11"/>
@@ -12587,7 +12712,7 @@
       <c r="R102" s="11"/>
       <c r="S102" s="11"/>
     </row>
-    <row r="103" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F103" s="11"/>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
@@ -12603,7 +12728,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="11"/>
     </row>
-    <row r="104" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F104" s="11"/>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
@@ -12619,7 +12744,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="11"/>
     </row>
-    <row r="105" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F105" s="11"/>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
@@ -12635,7 +12760,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="11"/>
     </row>
-    <row r="106" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
@@ -12651,7 +12776,7 @@
       <c r="R106" s="11"/>
       <c r="S106" s="11"/>
     </row>
-    <row r="107" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F107" s="11"/>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
@@ -12667,7 +12792,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="11"/>
     </row>
-    <row r="108" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F108" s="11"/>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
@@ -12683,7 +12808,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="11"/>
     </row>
-    <row r="109" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F109" s="11"/>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
@@ -12699,7 +12824,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="11"/>
     </row>
-    <row r="110" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F110" s="11"/>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
@@ -12715,7 +12840,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="11"/>
     </row>
-    <row r="111" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F111" s="11"/>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
@@ -12731,7 +12856,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="11"/>
     </row>
-    <row r="112" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F112" s="11"/>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
@@ -12747,7 +12872,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="11"/>
     </row>
-    <row r="113" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F113" s="11"/>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
@@ -12763,7 +12888,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="11"/>
     </row>
-    <row r="114" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F114" s="11"/>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
@@ -12779,7 +12904,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="11"/>
     </row>
-    <row r="115" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F115" s="11"/>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
@@ -12795,7 +12920,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="11"/>
     </row>
-    <row r="116" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F116" s="11"/>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
@@ -12811,7 +12936,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="11"/>
     </row>
-    <row r="117" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F117" s="11"/>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
@@ -12827,7 +12952,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="11"/>
     </row>
-    <row r="118" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F118" s="11"/>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
@@ -12843,7 +12968,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="11"/>
     </row>
-    <row r="119" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F119" s="11"/>
       <c r="G119" s="11"/>
       <c r="H119" s="11"/>
@@ -12859,7 +12984,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="11"/>
     </row>
-    <row r="120" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F120" s="11"/>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
@@ -12875,7 +13000,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="11"/>
     </row>
-    <row r="121" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F121" s="11"/>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
@@ -12891,7 +13016,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="11"/>
     </row>
-    <row r="122" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F122" s="11"/>
       <c r="G122" s="11"/>
       <c r="H122" s="11"/>
@@ -12907,7 +13032,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="11"/>
     </row>
-    <row r="123" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F123" s="11"/>
       <c r="G123" s="11"/>
       <c r="H123" s="11"/>
@@ -12923,7 +13048,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="11"/>
     </row>
-    <row r="124" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F124" s="11"/>
       <c r="G124" s="11"/>
       <c r="H124" s="11"/>
@@ -12939,7 +13064,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="11"/>
     </row>
-    <row r="125" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F125" s="11"/>
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
@@ -12955,7 +13080,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="11"/>
     </row>
-    <row r="126" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F126" s="11"/>
       <c r="G126" s="11"/>
       <c r="H126" s="11"/>
@@ -12971,7 +13096,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="11"/>
     </row>
-    <row r="127" spans="6:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F127" s="11"/>
       <c r="G127" s="11"/>
       <c r="H127" s="11"/>
@@ -12988,6 +13113,9 @@
       <c r="S127" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F87:H87"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
     <ignoredError sqref="A1:B1 A51:B51 A2:B2 A3:B3 A4:B4 A5:B5 A6:B6 A7:B7 A8:B8 A9:B9 A10:B10 A11:B11 A12:B12 A13:B13 A14:B14 A15:B15 A16:B16 A17:B17 A18:B18 A19:B19 A20:B20 A21:B21 A22:B22 A23:B23 A24:B24 A25:B25 A26:B26 A27:B27 A28:B28 A29:B29 A30:B30 A31:B31 A32:B32 A33:B33 A34:B34 A35:B35 A36:B36 A37:B37 A38:B38 A39:B39 A40:B40 A41:B41 A42:B42 A43:B43 A44:B44 A45:B45 A46:B46 A47:B47 A48:B48 A49:B49 A50:B50" numberStoredAsText="1"/>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Documents\GitHub\Arquivado\Faculdade\Terceiro Semestre\Estatística Aplicada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A2A302-6F73-4EA5-9D5F-F929B6F6F67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD85B3-EC7E-4DC6-9EBE-BEF4CD50DA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,7 @@
     <pivotCache cacheId="1" r:id="rId7"/>
     <pivotCache cacheId="2" r:id="rId8"/>
     <pivotCache cacheId="3" r:id="rId9"/>
+    <pivotCache cacheId="37" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -385,6 +386,36 @@
   <si>
     <t>x</t>
   </si>
+  <si>
+    <t>Contagem de Horas_Treinamento</t>
+  </si>
+  <si>
+    <t>14-19</t>
+  </si>
+  <si>
+    <t>26-31</t>
+  </si>
+  <si>
+    <t>32-37</t>
+  </si>
+  <si>
+    <t>38-43</t>
+  </si>
+  <si>
+    <t>44-49</t>
+  </si>
+  <si>
+    <t>50-55</t>
+  </si>
+  <si>
+    <t>56-61</t>
+  </si>
+  <si>
+    <t>62-67</t>
+  </si>
+  <si>
+    <t>68-73</t>
+  </si>
 </sst>
 </file>
 
@@ -558,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -661,6 +692,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6820,8 +6856,29 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>R:</a:t>
+            <a:t>R: Indica que não há homogeneidade e sim heterogeneidade, pois a</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> diferença entre a média e o desvio padrão é grande.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr lvl="0"/>
@@ -7931,6 +7988,143 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Elio Savoine" refreshedDate="46153.841847222226" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{C4657E9F-4774-4941-B6C1-E2C20656C0E6}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D51" sheet="Conjunto de Dados"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Área_Atuação" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Suporte"/>
+        <s v="Desenvolvimento"/>
+        <s v="Dados"/>
+        <s v="Infraestrutura"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Horas_Treinamento" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5" maxValue="40" count="37">
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="9.5"/>
+        <n v="12.5"/>
+        <n v="15.5"/>
+        <n v="17"/>
+        <n v="18.5"/>
+        <n v="20"/>
+        <n v="21.5"/>
+        <n v="15"/>
+        <n v="16.5"/>
+        <n v="18"/>
+        <n v="19.5"/>
+        <n v="21"/>
+        <n v="22.5"/>
+        <n v="24"/>
+        <n v="25.5"/>
+        <n v="27"/>
+        <n v="28.5"/>
+        <n v="6.5"/>
+        <n v="23"/>
+        <n v="24.5"/>
+        <n v="16"/>
+        <n v="17.5"/>
+        <n v="30"/>
+        <n v="40"/>
+        <n v="22"/>
+        <n v="26"/>
+        <n v="28"/>
+      </sharedItems>
+      <fieldGroup base="2">
+        <rangePr startNum="5" endNum="40" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;5"/>
+          <s v="5-15"/>
+          <s v="15-25"/>
+          <s v="25-35"/>
+          <s v="35-45"/>
+          <s v="&gt;45"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Tickets_Mês" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="14" maxValue="69" count="38">
+        <n v="14"/>
+        <n v="17"/>
+        <n v="19"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="33"/>
+        <n v="24"/>
+        <n v="27"/>
+        <n v="36"/>
+        <n v="39"/>
+        <n v="42"/>
+        <n v="45"/>
+        <n v="47"/>
+        <n v="35"/>
+        <n v="38"/>
+        <n v="41"/>
+        <n v="44"/>
+        <n v="49"/>
+        <n v="53"/>
+        <n v="55"/>
+        <n v="58"/>
+        <n v="61"/>
+        <n v="18"/>
+        <n v="28"/>
+        <n v="32"/>
+        <n v="43"/>
+        <n v="50"/>
+        <n v="37"/>
+        <n v="40"/>
+        <n v="65"/>
+        <n v="69"/>
+        <n v="48"/>
+        <n v="52"/>
+        <n v="60"/>
+      </sharedItems>
+      <fieldGroup base="3">
+        <rangePr startNum="14" endNum="69" groupInterval="6"/>
+        <groupItems count="12">
+          <s v="&lt;14"/>
+          <s v="14-19"/>
+          <s v="20-25"/>
+          <s v="26-31"/>
+          <s v="32-37"/>
+          <s v="38-43"/>
+          <s v="44-49"/>
+          <s v="50-55"/>
+          <s v="56-61"/>
+          <s v="62-67"/>
+          <s v="68-73"/>
+          <s v="&gt;74"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
   <r>
@@ -9147,6 +9341,311 @@
     <x v="1"/>
     <x v="36"/>
     <n v="60"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <s v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="5"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="6"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="7"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="8"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="9"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="10"/>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="11"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="12"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="13"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="14"/>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="15"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="16"/>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="17"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="18"/>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <s v="19"/>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <s v="20"/>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <s v="21"/>
+    <x v="2"/>
+    <x v="17"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <s v="22"/>
+    <x v="2"/>
+    <x v="18"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <s v="23"/>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <s v="24"/>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <s v="25"/>
+    <x v="2"/>
+    <x v="21"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <s v="26"/>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <s v="27"/>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <s v="28"/>
+    <x v="2"/>
+    <x v="24"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <s v="29"/>
+    <x v="2"/>
+    <x v="25"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <s v="30"/>
+    <x v="2"/>
+    <x v="26"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <s v="31"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <s v="32"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="33"/>
+    <x v="3"/>
+    <x v="10"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="34"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <s v="35"/>
+    <x v="3"/>
+    <x v="11"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="36"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <s v="37"/>
+    <x v="3"/>
+    <x v="12"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <s v="38"/>
+    <x v="3"/>
+    <x v="13"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <s v="39"/>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <s v="40"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <s v="41"/>
+    <x v="1"/>
+    <x v="28"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <s v="42"/>
+    <x v="1"/>
+    <x v="29"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <s v="43"/>
+    <x v="0"/>
+    <x v="30"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <s v="44"/>
+    <x v="0"/>
+    <x v="31"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <s v="45"/>
+    <x v="2"/>
+    <x v="32"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <s v="46"/>
+    <x v="2"/>
+    <x v="33"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <s v="47"/>
+    <x v="3"/>
+    <x v="34"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <s v="48"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <s v="49"/>
+    <x v="0"/>
+    <x v="35"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <s v="50"/>
+    <x v="1"/>
+    <x v="36"/>
+    <x v="37"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -9615,6 +10114,105 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F89E28B-7F1E-4783-A447-97608E76ECA1}" name="Tabela dinâmica6" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A15:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" numFmtId="1" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de Horas_Treinamento" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0D9A32C-61A1-4FB1-A7DC-EC8CE499D156}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
@@ -10637,14 +11235,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D9EBD1-B91E-419B-88E1-89223DF55B6B}">
-  <dimension ref="A3:F12"/>
+  <dimension ref="A3:F26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10817,6 +11416,102 @@
       </c>
       <c r="F12" s="12">
         <v>16.86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="36">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Tarefa - CR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Documents\GitHub\Arquivado\Faculdade\Terceiro Semestre\Estatística Aplicada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD85B3-EC7E-4DC6-9EBE-BEF4CD50DA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102416F8-54A0-4D48-88CB-176B84F79C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Areá_Atuação" sheetId="2" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <definedName name="_xlchart.v1.0" hidden="1">Horas_Treinamento!$A$12:$A$15</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Horas_Treinamento!$B$11</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Horas_Treinamento!$B$12:$B$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Conjunto de Dados'!$C$2:$C$51</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Conjunto de Dados'!$D$2:$D$51</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Conjunto de Dados'!$C$2:$C$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -32,7 +32,7 @@
     <pivotCache cacheId="1" r:id="rId7"/>
     <pivotCache cacheId="2" r:id="rId8"/>
     <pivotCache cacheId="3" r:id="rId9"/>
-    <pivotCache cacheId="37" r:id="rId10"/>
+    <pivotCache cacheId="4" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -387,9 +387,6 @@
     <t>x</t>
   </si>
   <si>
-    <t>Contagem de Horas_Treinamento</t>
-  </si>
-  <si>
     <t>14-19</t>
   </si>
   <si>
@@ -415,6 +412,9 @@
   </si>
   <si>
     <t>68-73</t>
+  </si>
+  <si>
+    <t>Média de Tickets_Mês</t>
   </si>
 </sst>
 </file>
@@ -589,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -693,16 +693,221 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="131">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -2457,7 +2662,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2522,7 +2727,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -5974,8 +6179,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3600450" y="533400"/>
-              <a:ext cx="5276850" cy="2936875"/>
+              <a:off x="3575050" y="527050"/>
+              <a:ext cx="5073650" cy="2882900"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6856,7 +7061,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>R: Indica que não há homogeneidade e sim heterogeneidade, pois a</a:t>
+            <a:t>R: A área que há</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" baseline="0">
@@ -6868,20 +7073,39 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> diferença entre a média e o desvio padrão é grande.</a:t>
+            <a:t> maior quantidade de Tickets é a área de dados. Não há homogeneidade na carga de trabalho.</a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
         </a:p>
         <a:p>
-          <a:pPr lvl="0"/>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:endParaRPr lang="pt-BR" sz="1200" b="1">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -7559,8 +7783,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10927643" y="10419645"/>
-              <a:ext cx="4749095" cy="2775303"/>
+              <a:off x="10692693" y="10254545"/>
+              <a:ext cx="4596695" cy="2734028"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7637,8 +7861,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="16705084" y="10440812"/>
-              <a:ext cx="4730045" cy="2777772"/>
+              <a:off x="16314559" y="10275712"/>
+              <a:ext cx="4552245" cy="2733322"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9707,26 +9931,26 @@
     <dataField name="fa" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="61">
+    <format dxfId="130">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="129">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="128">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="126">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="125">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -9737,26 +9961,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="124">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="123">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="122">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="121">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="119">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -9847,19 +10071,19 @@
     <dataField name="fa" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="1"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="49">
+    <format dxfId="118">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="117">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="116">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="115">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="114">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="4">
@@ -9871,10 +10095,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="113">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="112">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -9885,7 +10109,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="111">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -9894,16 +10118,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="110">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="109">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="108">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="4">
@@ -9915,10 +10139,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="105">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -10017,16 +10241,16 @@
     <dataField name="fa" fld="3" subtotal="count" showDataAs="runTotal" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="35">
+    <format dxfId="104">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="103">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="102">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="6">
@@ -10040,10 +10264,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="100">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="99">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -10054,16 +10278,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="98">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="97">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="96">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="6">
@@ -10077,10 +10301,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -10091,7 +10315,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="92">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10114,105 +10338,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F89E28B-7F1E-4783-A447-97608E76ECA1}" name="Tabela dinâmica6" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A15:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" numFmtId="1" showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de Horas_Treinamento" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0D9A32C-61A1-4FB1-A7DC-EC8CE499D156}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
@@ -10295,25 +10420,25 @@
     <dataField name="Média de Horas_Treinamento" fld="2" subtotal="average" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="23">
-    <format dxfId="22">
+    <format dxfId="91">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="90">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="89">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="88">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="87">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="86">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -10328,38 +10453,38 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="84">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="83">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="82">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="81">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="80">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="79">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="78">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="77">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="76">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -10374,27 +10499,27 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="71">
       <pivotArea field="1" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" selected="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="70">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -10406,11 +10531,305 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="69">
       <pivotArea field="2" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
             <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F89E28B-7F1E-4783-A447-97608E76ECA1}" name="Tabela dinâmica6" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A15:F27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" numFmtId="1" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Tickets_Mês" fld="3" subtotal="average" baseField="3" baseItem="1"/>
+  </dataFields>
+  <formats count="27">
+    <format dxfId="68">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="66">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="64">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="10">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="59">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="55">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="10">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="51">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="49">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="3">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea field="3" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="3">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="3" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea field="3" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea field="1" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="3" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -10751,15 +11170,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE768767-D7B5-4940-ACE8-9C4982467EE3}">
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>62</v>
       </c>
@@ -10773,7 +11192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>37</v>
       </c>
@@ -10787,7 +11206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>26</v>
       </c>
@@ -10801,7 +11220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>44</v>
       </c>
@@ -10815,7 +11234,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
@@ -10829,7 +11248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>58</v>
       </c>
@@ -10841,7 +11260,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>62</v>
       </c>
@@ -10849,7 +11268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>37</v>
       </c>
@@ -10857,7 +11276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
@@ -10865,7 +11284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>44</v>
       </c>
@@ -10873,7 +11292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>5</v>
       </c>
@@ -10881,7 +11300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18" t="s">
         <v>58</v>
       </c>
@@ -10898,7 +11317,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1FA8A1-06B5-4FF8-8B14-81C20D53ECC7}">
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
@@ -10906,7 +11325,7 @@
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
@@ -10920,7 +11339,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
         <v>63</v>
       </c>
@@ -10934,7 +11353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>64</v>
       </c>
@@ -10948,7 +11367,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>65</v>
       </c>
@@ -10962,7 +11381,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
         <v>66</v>
       </c>
@@ -10976,7 +11395,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>58</v>
       </c>
@@ -10988,7 +11407,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>3</v>
       </c>
@@ -10996,7 +11415,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>63</v>
       </c>
@@ -11004,7 +11423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>64</v>
       </c>
@@ -11012,7 +11431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>65</v>
       </c>
@@ -11020,7 +11439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21" t="s">
         <v>66</v>
       </c>
@@ -11028,7 +11447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
         <v>58</v>
       </c>
@@ -11045,15 +11464,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA27BDE-5BEF-44E2-8E70-AEAC1839CC4C}">
   <dimension ref="A3:D20"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -11067,7 +11486,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>67</v>
       </c>
@@ -11081,7 +11500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>68</v>
       </c>
@@ -11095,7 +11514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
         <v>69</v>
       </c>
@@ -11109,7 +11528,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>70</v>
       </c>
@@ -11123,7 +11542,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
         <v>71</v>
       </c>
@@ -11137,7 +11556,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
         <v>72</v>
       </c>
@@ -11151,7 +11570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="23" t="s">
         <v>58</v>
       </c>
@@ -11163,7 +11582,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>2</v>
       </c>
@@ -11171,7 +11590,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="24" t="s">
         <v>67</v>
       </c>
@@ -11179,7 +11598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
         <v>68</v>
       </c>
@@ -11187,7 +11606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="24" t="s">
         <v>69</v>
       </c>
@@ -11195,7 +11614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>70</v>
       </c>
@@ -11203,7 +11622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="24" t="s">
         <v>71</v>
       </c>
@@ -11211,7 +11630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24" t="s">
         <v>72</v>
       </c>
@@ -11219,7 +11638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="16" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A20" s="25" t="s">
         <v>58</v>
       </c>
@@ -11235,18 +11654,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D9EBD1-B91E-419B-88E1-89223DF55B6B}">
-  <dimension ref="A3:F26"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:F27"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.75" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>82</v>
       </c>
@@ -11258,7 +11677,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>80</v>
       </c>
@@ -11278,7 +11697,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>83</v>
       </c>
@@ -11296,7 +11715,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>84</v>
       </c>
@@ -11314,7 +11733,7 @@
         <v>12.272727272727273</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
         <v>85</v>
       </c>
@@ -11334,7 +11753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>86</v>
       </c>
@@ -11352,7 +11771,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
         <v>87</v>
       </c>
@@ -11370,7 +11789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>88</v>
       </c>
@@ -11384,7 +11803,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
         <v>89</v>
       </c>
@@ -11398,7 +11817,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
         <v>58</v>
       </c>
@@ -11418,100 +11837,230 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="23" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12">
+        <v>18</v>
+      </c>
+      <c r="E17" s="20">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="F17" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12">
+        <v>23</v>
+      </c>
+      <c r="D18" s="12">
+        <v>22.5</v>
+      </c>
+      <c r="E18" s="20">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="F18" s="20">
+        <v>22.714285714285715</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="36">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12">
+        <v>28.5</v>
+      </c>
+      <c r="D19" s="12">
+        <v>28.5</v>
+      </c>
+      <c r="E19" s="20">
+        <v>28.333333333333332</v>
+      </c>
+      <c r="F19" s="20">
+        <v>28.428571428571427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="B20" s="12">
+        <v>35</v>
+      </c>
+      <c r="C20" s="12">
+        <v>34.5</v>
+      </c>
+      <c r="D20" s="12">
+        <v>33.5</v>
+      </c>
+      <c r="E20" s="12">
+        <v>35</v>
+      </c>
+      <c r="F20" s="20">
+        <v>34.428571428571431</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="B21" s="12">
+        <v>39.5</v>
+      </c>
+      <c r="C21" s="12">
+        <v>40.5</v>
+      </c>
+      <c r="D21" s="20">
+        <v>40.666666666666664</v>
+      </c>
+      <c r="E21" s="12">
+        <v>40</v>
+      </c>
+      <c r="F21" s="12">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="36">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="B22" s="20">
+        <v>46.666666666666664</v>
+      </c>
+      <c r="C22" s="12">
+        <v>46</v>
+      </c>
+      <c r="D22" s="12">
+        <v>48</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="20">
+        <v>46.666666666666664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="36">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
+      <c r="B23" s="12">
+        <v>54</v>
+      </c>
+      <c r="C23" s="12">
+        <v>51.5</v>
+      </c>
+      <c r="D23" s="12">
+        <v>52</v>
+      </c>
+      <c r="E23" s="12">
+        <v>55</v>
+      </c>
+      <c r="F23" s="12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="36">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+      <c r="B24" s="12">
+        <v>59.5</v>
+      </c>
+      <c r="C24" s="12">
+        <v>60</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="20">
+        <v>59.666666666666664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
+      <c r="B25" s="12">
+        <v>65</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
+      <c r="B26" s="12">
+        <v>69</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="36">
-        <v>50</v>
+      <c r="B27" s="12">
+        <v>51.25</v>
+      </c>
+      <c r="C27" s="20">
+        <v>39.07692307692308</v>
+      </c>
+      <c r="D27" s="20">
+        <v>34.083333333333336</v>
+      </c>
+      <c r="E27" s="20">
+        <v>28.307692307692307</v>
+      </c>
+      <c r="F27" s="12">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -11522,17 +12071,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB127"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8.625" customWidth="1"/>
+    <col min="6" max="6" width="8.58203125" customWidth="1"/>
     <col min="15" max="15" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="18.125" customWidth="1"/>
+    <col min="21" max="21" width="18.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -11546,7 +12095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11560,7 +12109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -11574,7 +12123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -11588,7 +12137,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -11602,7 +12151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -11616,7 +12165,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -11630,7 +12179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -11644,7 +12193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -11658,7 +12207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -11672,7 +12221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -11686,7 +12235,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -11700,7 +12249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -11714,7 +12263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -11728,7 +12277,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -11742,7 +12291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -11756,7 +12305,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -11770,7 +12319,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -11784,7 +12333,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -11798,7 +12347,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -11812,7 +12361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -11826,7 +12375,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -11840,7 +12389,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -11854,7 +12403,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -11868,7 +12417,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
@@ -11882,7 +12431,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>14</v>
       </c>
@@ -11896,7 +12445,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
@@ -11910,7 +12459,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
@@ -11924,7 +12473,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
@@ -11938,7 +12487,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
@@ -11952,7 +12501,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -11966,7 +12515,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
@@ -11980,7 +12529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
@@ -11994,7 +12543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -12008,7 +12557,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -12022,7 +12571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -12036,7 +12585,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -12050,7 +12599,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
@@ -12064,7 +12613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -12078,7 +12627,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -12092,7 +12641,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -12111,7 +12660,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -12130,7 +12679,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -12149,7 +12698,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -12174,7 +12723,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -12199,7 +12748,7 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -12224,7 +12773,7 @@
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -12249,7 +12798,7 @@
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -12274,7 +12823,7 @@
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -12299,7 +12848,7 @@
       <c r="O49" s="11"/>
       <c r="P49" s="11"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -12324,7 +12873,7 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>57</v>
       </c>
@@ -12349,7 +12898,7 @@
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F52" s="26">
         <v>4</v>
       </c>
@@ -12372,7 +12921,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F53" s="11"/>
       <c r="G53" s="28" t="s">
         <v>73</v>
@@ -12403,7 +12952,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F54" s="28" t="s">
         <v>78</v>
       </c>
@@ -12442,7 +12991,7 @@
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
       <c r="H55" s="28">
@@ -12463,7 +13012,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="11"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F56" s="11"/>
       <c r="G56" s="11"/>
       <c r="H56" s="31">
@@ -12481,7 +13030,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F57" s="28" t="s">
         <v>79</v>
       </c>
@@ -12518,7 +13067,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="11"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
       <c r="H58" s="32">
@@ -12536,7 +13085,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
       <c r="H59" s="28">
@@ -12554,7 +13103,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F60" s="11"/>
       <c r="G60" s="11"/>
       <c r="H60" s="28">
@@ -12572,7 +13121,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
       <c r="H61" s="28">
@@ -12590,7 +13139,7 @@
       <c r="U61" s="11"/>
       <c r="V61" s="11"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F62" s="11"/>
       <c r="G62" s="11"/>
       <c r="H62" s="28">
@@ -12608,7 +13157,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
       <c r="H63" s="28">
@@ -12626,7 +13175,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F64" s="11"/>
       <c r="G64" s="11"/>
       <c r="H64" s="28">
@@ -12644,7 +13193,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="11"/>
     </row>
-    <row r="65" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
       <c r="H65" s="28">
@@ -12662,7 +13211,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
     </row>
-    <row r="66" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="H66" s="28">
@@ -12680,7 +13229,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F67" s="11"/>
       <c r="G67" s="11"/>
       <c r="H67" s="28">
@@ -12698,7 +13247,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F68" s="11"/>
       <c r="G68" s="11"/>
       <c r="H68" s="28">
@@ -12728,7 +13277,7 @@
       </c>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:28" x14ac:dyDescent="0.35">
       <c r="O69" s="28" t="s">
         <v>78</v>
       </c>
@@ -12759,7 +13308,7 @@
       <c r="AA69" s="11"/>
       <c r="AB69" s="11"/>
     </row>
-    <row r="70" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:28" x14ac:dyDescent="0.35">
       <c r="O70" s="28" t="s">
         <v>79</v>
       </c>
@@ -12787,7 +13336,7 @@
       <c r="AA70" s="11"/>
       <c r="AB70" s="11"/>
     </row>
-    <row r="71" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:28" x14ac:dyDescent="0.35">
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
       <c r="R71" s="11"/>
@@ -12802,7 +13351,7 @@
       <c r="AA71" s="11"/>
       <c r="AB71" s="11"/>
     </row>
-    <row r="72" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F72" s="26">
         <v>7</v>
       </c>
@@ -12829,7 +13378,7 @@
       <c r="AA72" s="11"/>
       <c r="AB72" s="11"/>
     </row>
-    <row r="73" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F73" s="11"/>
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
@@ -12854,7 +13403,7 @@
       <c r="AA73" s="11"/>
       <c r="AB73" s="11"/>
     </row>
-    <row r="74" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F74" s="11"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
@@ -12879,7 +13428,7 @@
       <c r="AA74" s="11"/>
       <c r="AB74" s="11"/>
     </row>
-    <row r="75" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F75" s="11"/>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
@@ -12904,7 +13453,7 @@
       <c r="AA75" s="11"/>
       <c r="AB75" s="11"/>
     </row>
-    <row r="76" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F76" s="11"/>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
@@ -12929,7 +13478,7 @@
       <c r="AA76" s="11"/>
       <c r="AB76" s="11"/>
     </row>
-    <row r="77" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F77" s="11"/>
       <c r="G77" s="11"/>
       <c r="H77" s="11"/>
@@ -12954,7 +13503,7 @@
       <c r="AA77" s="11"/>
       <c r="AB77" s="11"/>
     </row>
-    <row r="78" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F78" s="11"/>
       <c r="G78" s="11"/>
       <c r="H78" s="11"/>
@@ -12979,7 +13528,7 @@
       <c r="AA78" s="11"/>
       <c r="AB78" s="11"/>
     </row>
-    <row r="79" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F79" s="11"/>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
@@ -13004,7 +13553,7 @@
       <c r="AA79" s="11"/>
       <c r="AB79" s="11"/>
     </row>
-    <row r="80" spans="6:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F80" s="11"/>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
@@ -13029,7 +13578,7 @@
       <c r="AA80" s="11"/>
       <c r="AB80" s="11"/>
     </row>
-    <row r="81" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F81" s="11"/>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
@@ -13045,7 +13594,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="11"/>
     </row>
-    <row r="82" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F82" s="11"/>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
@@ -13061,7 +13610,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="11"/>
     </row>
-    <row r="83" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F83" s="11"/>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
@@ -13077,7 +13626,7 @@
       <c r="R83" s="11"/>
       <c r="S83" s="11"/>
     </row>
-    <row r="84" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F84" s="11"/>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
@@ -13093,7 +13642,7 @@
       <c r="R84" s="11"/>
       <c r="S84" s="11"/>
     </row>
-    <row r="85" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F85" s="11"/>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
@@ -13109,7 +13658,7 @@
       <c r="R85" s="11"/>
       <c r="S85" s="11"/>
     </row>
-    <row r="86" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F86" s="11"/>
       <c r="G86" s="11"/>
       <c r="H86" s="11"/>
@@ -13125,12 +13674,12 @@
       <c r="R86" s="11"/>
       <c r="S86" s="11"/>
     </row>
-    <row r="87" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="F87" s="34" t="s">
+    <row r="87" spans="6:19" x14ac:dyDescent="0.35">
+      <c r="F87" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
       <c r="I87" s="28">
         <f>CORREL(C2:C51,D2:D51)</f>
         <v>0.99001168508891357</v>
@@ -13147,7 +13696,7 @@
       <c r="R87" s="11"/>
       <c r="S87" s="11"/>
     </row>
-    <row r="88" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F88" s="11"/>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
@@ -13163,7 +13712,7 @@
       <c r="R88" s="11"/>
       <c r="S88" s="11"/>
     </row>
-    <row r="89" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F89" s="11"/>
       <c r="G89" s="11"/>
       <c r="H89" s="11" t="s">
@@ -13187,7 +13736,7 @@
       <c r="R89" s="11"/>
       <c r="S89" s="11"/>
     </row>
-    <row r="90" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F90" s="11"/>
       <c r="G90" s="11" t="s">
         <v>99</v>
@@ -13215,7 +13764,7 @@
       <c r="R90" s="11"/>
       <c r="S90" s="11"/>
     </row>
-    <row r="91" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F91" s="11"/>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
@@ -13231,7 +13780,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="11"/>
     </row>
-    <row r="92" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F92" s="11"/>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
@@ -13247,7 +13796,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="11"/>
     </row>
-    <row r="93" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F93" s="11"/>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
@@ -13263,7 +13812,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="11"/>
     </row>
-    <row r="94" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F94" s="11"/>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
@@ -13279,7 +13828,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="11"/>
     </row>
-    <row r="95" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F95" s="11"/>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
@@ -13295,7 +13844,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="11"/>
     </row>
-    <row r="96" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F96" s="11"/>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -13311,7 +13860,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="11"/>
     </row>
-    <row r="97" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F97" s="11"/>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
@@ -13327,7 +13876,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="11"/>
     </row>
-    <row r="98" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
@@ -13343,7 +13892,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="11"/>
     </row>
-    <row r="99" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F99" s="11"/>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
@@ -13359,7 +13908,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="11"/>
     </row>
-    <row r="100" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F100" s="11"/>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
@@ -13375,7 +13924,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="11"/>
     </row>
-    <row r="101" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F101" s="11"/>
       <c r="G101" s="11"/>
       <c r="H101" s="11"/>
@@ -13391,7 +13940,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="11"/>
     </row>
-    <row r="102" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F102" s="11"/>
       <c r="G102" s="11"/>
       <c r="H102" s="11"/>
@@ -13407,7 +13956,7 @@
       <c r="R102" s="11"/>
       <c r="S102" s="11"/>
     </row>
-    <row r="103" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F103" s="11"/>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
@@ -13423,7 +13972,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="11"/>
     </row>
-    <row r="104" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F104" s="11"/>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
@@ -13439,7 +13988,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="11"/>
     </row>
-    <row r="105" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F105" s="11"/>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
@@ -13455,7 +14004,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="11"/>
     </row>
-    <row r="106" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
@@ -13471,7 +14020,7 @@
       <c r="R106" s="11"/>
       <c r="S106" s="11"/>
     </row>
-    <row r="107" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F107" s="11"/>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
@@ -13487,7 +14036,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="11"/>
     </row>
-    <row r="108" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F108" s="11"/>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
@@ -13503,7 +14052,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="11"/>
     </row>
-    <row r="109" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F109" s="11"/>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
@@ -13519,7 +14068,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="11"/>
     </row>
-    <row r="110" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F110" s="11"/>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
@@ -13535,7 +14084,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="11"/>
     </row>
-    <row r="111" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F111" s="11"/>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
@@ -13551,7 +14100,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="11"/>
     </row>
-    <row r="112" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F112" s="11"/>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
@@ -13567,7 +14116,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="11"/>
     </row>
-    <row r="113" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F113" s="11"/>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
@@ -13583,7 +14132,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="11"/>
     </row>
-    <row r="114" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F114" s="11"/>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
@@ -13599,7 +14148,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="11"/>
     </row>
-    <row r="115" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F115" s="11"/>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
@@ -13615,7 +14164,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="11"/>
     </row>
-    <row r="116" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F116" s="11"/>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
@@ -13631,7 +14180,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="11"/>
     </row>
-    <row r="117" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F117" s="11"/>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
@@ -13647,7 +14196,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="11"/>
     </row>
-    <row r="118" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F118" s="11"/>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
@@ -13663,7 +14212,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="11"/>
     </row>
-    <row r="119" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F119" s="11"/>
       <c r="G119" s="11"/>
       <c r="H119" s="11"/>
@@ -13679,7 +14228,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="11"/>
     </row>
-    <row r="120" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F120" s="11"/>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
@@ -13695,7 +14244,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="11"/>
     </row>
-    <row r="121" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F121" s="11"/>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
@@ -13711,7 +14260,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="11"/>
     </row>
-    <row r="122" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F122" s="11"/>
       <c r="G122" s="11"/>
       <c r="H122" s="11"/>
@@ -13727,7 +14276,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="11"/>
     </row>
-    <row r="123" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F123" s="11"/>
       <c r="G123" s="11"/>
       <c r="H123" s="11"/>
@@ -13743,7 +14292,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="11"/>
     </row>
-    <row r="124" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F124" s="11"/>
       <c r="G124" s="11"/>
       <c r="H124" s="11"/>
@@ -13759,7 +14308,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="11"/>
     </row>
-    <row r="125" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F125" s="11"/>
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
@@ -13775,7 +14324,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="11"/>
     </row>
-    <row r="126" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F126" s="11"/>
       <c r="G126" s="11"/>
       <c r="H126" s="11"/>
@@ -13791,7 +14340,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="11"/>
     </row>
-    <row r="127" spans="6:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="6:19" x14ac:dyDescent="0.35">
       <c r="F127" s="11"/>
       <c r="G127" s="11"/>
       <c r="H127" s="11"/>
